--- a/output/pdf_financials_xlsx/ETR.xlsx
+++ b/output/pdf_financials_xlsx/ETR.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003727</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002062</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00638</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.455637</v>
+        <v>-0.459364</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.541615</v>
+        <v>-0.543677</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.802906</v>
+        <v>-1.809286</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.436106</v>
+        <v>-0.439833</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.523245</v>
+        <v>-0.525307</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.784785</v>
+        <v>-1.791165</v>
       </c>
     </row>
     <row r="30">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02025</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02025</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.020758</v>
       </c>
     </row>
     <row r="125">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02025</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02025</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.020758</v>
       </c>
     </row>
     <row r="126">
@@ -2842,7 +2842,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n">
         <v>0.0249</v>
       </c>
@@ -3910,7 +3914,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>-0.02025</v>
       </c>
@@ -4606,7 +4614,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">

--- a/output/pdf_financials_xlsx/ETR.xlsx
+++ b/output/pdf_financials_xlsx/ETR.xlsx
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0425</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="68">
@@ -3852,7 +3852,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4164,7 +4168,11 @@
           <t>Share subscriptions- private placement</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.09</v>
       </c>
